--- a/dist-test/unit-test-report.xlsx
+++ b/dist-test/unit-test-report.xlsx
@@ -410,7 +410,7 @@
         <v>Generated on:</v>
       </c>
       <c r="B2" t="str">
-        <v>22/6/2026, 2:17:48 pm</v>
+        <v>22/6/2026, 2:30:09 pm</v>
       </c>
     </row>
     <row r="4">
@@ -845,7 +845,7 @@
         <v>PASS</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -949,7 +949,7 @@
         <v>PASS</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1599,7 +1599,7 @@
         <v>PASS</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3159,7 +3159,7 @@
         <v>PASS</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3523,7 +3523,7 @@
         <v>PASS</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
